--- a/naver-place-crawler/results_nail/김포_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/김포_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V240"/>
+  <dimension ref="A1:V298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22649,29 +22649,29 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>속눈썹증모,연장</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>사월</t>
+          <t>미젤네일</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>zioxx@naver.com</t>
+          <t>94105842@naver.com</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>0507-1416-9944</t>
+          <t>0507-1426-0819</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>경기도 김포시 고촌읍 태리로 285 5층 506호</t>
+          <t>경기도 김포시 초당로61번길 5 101호</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -22711,13 +22711,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="Q239" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -22726,12 +22726,12 @@
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>1147960403</t>
+          <t>2052162321</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147960403</t>
+          <t>https://m.place.naver.com/place/2052162321</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
@@ -22743,34 +22743,34 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>피부,체형관리</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>피부미인손발미인</t>
+          <t>제이썸네일</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>bogdongyi66@naver.com</t>
+          <t>52211004@naver.com</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>0507-1417-9073</t>
+          <t>031-008-0000</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강2로 103 우남퍼스트빌</t>
+          <t>경기도 김포시 대곶면 대곶남로501번안길 20-9</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bogdongyi66</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -22780,12 +22780,12 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -22805,30 +22805,5330 @@
         </is>
       </c>
       <c r="P240" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>7</v>
+      </c>
+      <c r="R240" t="n">
+        <v>15</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>1269113013</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1269113013</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>네일모아 김포풍무점</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>jiyoon5690@naver.com</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>0507-1316-4829</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>경기도 김포시 풍무로 2 유현마을신동아아파트 상가 203호</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_SfNbG</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>90</v>
+      </c>
+      <c r="R241" t="n">
+        <v>302</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>1034764527</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1034764527</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>희한네일</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>myvalentineday@naver.com</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>0507-1427-7036</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>경기도 김포시 유현로237번길 88 116호 희한네일</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/heehan.nail</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>0</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>2034528143</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2034528143</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>네일은여기</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>herenail2102@naver.com</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>0507-1390-5088</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>경기도 김포시 솔터로 22 에비뉴스완 상가동 2층 236호 (예미지아파트상가)</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailist_juni</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>13</v>
+      </c>
+      <c r="R243" t="n">
+        <v>266</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>1458428963</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1458428963</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>제이비네일</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>wooaoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>0507-1380-9048</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>경기도 김포시 중봉1로 10 가동 3층</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/Jb___Nail</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>38</v>
+      </c>
+      <c r="R244" t="n">
+        <v>179</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>1200165348</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1200165348</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>네일그리다</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>basic39@naver.com</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>0507-1445-8921</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>경기도 김포시 풍무2로 33 201호</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/basic39</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>44</v>
+      </c>
+      <c r="R245" t="n">
+        <v>171</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>1751713902</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1751713902</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>예쁜데</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>yeppeunde@naver.com</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>0507-1366-1548</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강1로 250 108호</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ye_ppeun_de_lash</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>453</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>19</v>
+      </c>
+      <c r="R246" t="n">
+        <v>472</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>1274995204</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1274995204</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>아름네일&amp;오로지푸스 김포사우점</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>arumnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>0507-1307-2689</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포대로926번길 88-27 상가 1층 109호</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aaarum._.nail</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>1</v>
+      </c>
+      <c r="R247" t="n">
+        <v>14</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>2006904560</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2006904560</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>디에고푸스 김포점 예담, 예쁨을담다</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>goeun204@naver.com</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>0507-1328-4613</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>경기도 김포시 태장로 784 1층</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goeun204</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>63</v>
+      </c>
+      <c r="R248" t="n">
+        <v>226</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>1227795807</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1227795807</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>눈이부심</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>boping@naver.com</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>0507-1345-6283</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강9로75번길 190 이너매스한강 4층 416호 눈이부심</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/boping</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>837</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>56</v>
+      </c>
+      <c r="R249" t="n">
+        <v>893</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>1202720397</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1202720397</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>장기동네일홀릭</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>wanny2003@naver.com</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>0507-1356-9875</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강4로135번길 11 104호</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailholic_janggi</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>60</v>
+      </c>
+      <c r="R250" t="n">
+        <v>202</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>1419793869</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1419793869</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>크리스탈네일</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>seomiyoung700@naver.com</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>경기도 김포시 풍무로 34 상가동 101호</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>http://instagram.com/crystal777_nail</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>1</v>
+      </c>
+      <c r="R251" t="n">
+        <v>1</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>1418728084</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1418728084</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>려헤어네일아트 장기동점</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>dustn107@naver.com</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>031-981-9457</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강4로 176 2층</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>0</v>
+      </c>
+      <c r="R252" t="n">
+        <v>17</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>1930358737</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1930358737</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>수네일</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>yjh1000j@naver.com</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>031-996-8860</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>경기도 김포시 관순로 23</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>8</v>
+      </c>
+      <c r="R253" t="n">
+        <v>8</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>1257271333</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1257271333</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>꼼지락네일&amp;속눈썹</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>totosieun@naver.com</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>경기도 김포시 양촌읍 양곡1로56번길 28 가동 2층 203호</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/ggom_ji_rak_nail</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>9</v>
+      </c>
+      <c r="R254" t="n">
+        <v>197</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>1818060240</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1818060240</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>다미네일</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>290eun@naver.com</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>0507-1346-1639</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강11로255번길 149 상가동 101-1호</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/daminail1004</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>0</v>
+      </c>
+      <c r="R255" t="n">
+        <v>8</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>1641784249</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1641784249</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>로랑뷰티 네일&amp;왁싱 김포마산점</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>laurent_beauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>0507-1376-5472</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강8로194번길 130 1층 103호</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/laurent_beauty</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>245</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>36</v>
+      </c>
+      <c r="R256" t="n">
+        <v>281</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>1294009815</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1294009815</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>럭스네일&amp;속눈썹</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>tnt9175@naver.com</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>0507-1336-3348</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>경기도 김포시 풍무로 62 한화프라자 2층 204호</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luxe_nail_salon/</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>885</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>10</v>
+      </c>
+      <c r="R257" t="n">
+        <v>895</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>1169015313</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1169015313</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>오로라</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>iamewp@naver.com</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>경기도 김포시 고촌읍 인향로24번길 46 B동 101호 일부호</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aurora1109_</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P258" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>0</v>
+      </c>
+      <c r="R258" t="n">
+        <v>17</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>1421767696</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1421767696</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>다올네일</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>cho12113@naver.com</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>0507-1339-7205</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>경기도 김포시 유현로 52 프라임빌상가 1층 140호 다올네일</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/daol.nail</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>8</v>
+      </c>
+      <c r="R259" t="n">
+        <v>151</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>1389720206</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1389720206</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>네일하니</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>khh3311@naver.com</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>0507-1383-7819</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>경기도 김포시 초당로61번길 8 1층 네일하니</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail._.hani._</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>74</v>
+      </c>
+      <c r="R260" t="n">
+        <v>205</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>1306651286</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1306651286</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>네일라</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>0507-1388-0866</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>경기도 김포시 걸포2로 45 S2-A동 110호</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>19</v>
+      </c>
+      <c r="R261" t="n">
+        <v>36</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>1834021137</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1834021137</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>네일미</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>031-986-0107</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강4로 507 계림엠스퀘어 1층</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>4</v>
+      </c>
+      <c r="R262" t="n">
+        <v>9</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>485601910</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/485601910</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>위시리브네일</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>0507-1440-4802</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강9로75번길 10 6층 602-B호</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ibwIX</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>11</v>
+      </c>
+      <c r="R263" t="n">
+        <v>54</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>2084801983</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084801983</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>쏭's네일</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강7로22번길 174-48 103호</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ssong_s_nail</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>6</v>
+      </c>
+      <c r="R264" t="n">
+        <v>182</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>1098812930</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1098812930</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>유어인 네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>0507-1324-1228</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>경기도 김포시 고촌읍 태리로 293 베스트프라자 305호</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/your_inn_nailstudio</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>2</v>
+      </c>
+      <c r="R265" t="n">
+        <v>190</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>1951415191</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1951415191</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>NAIL NEURU 김포점</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>0507-1474-0934</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강8로194번길 20-6 1층 102호</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailneuru</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>771</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>59</v>
+      </c>
+      <c r="R266" t="n">
+        <v>830</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>1753257601</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1753257601</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>라비나네일</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>031-996-6776</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>경기도 김포시 태장로 820 1층 103호</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>http://instagram.com/lavina_nail</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>6</v>
+      </c>
+      <c r="R267" t="n">
+        <v>56</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>555426214</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/555426214</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>네일바오</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>n_bao@naver.com</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>경기도 김포시 태장로 823 자이에비뉴 206호 네일바오</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://nailbao.creatorlink.net/</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>229</v>
+      </c>
+      <c r="R268" t="n">
+        <v>252</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>306688201</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/306688201</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>오브유 네일</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>td2369@naver.com</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>0507-1373-0746</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강1로 227 5층</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/td2369</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>435</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>7</v>
+      </c>
+      <c r="R269" t="n">
+        <v>442</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>1502216184</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1502216184</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>피카손</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>picason5124@naver.com</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>0507-1309-5124</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강1로 250 골든타임 2층 205호</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/picason5124</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>1144</v>
+      </c>
+      <c r="R270" t="n">
+        <v>1348</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>1358739278</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1358739278</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>네일프랜디 김포구래점</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>0507-1445-0812</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강9로75번길 22 603-1호</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/nail.frendi</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>77</v>
+      </c>
+      <c r="R271" t="n">
+        <v>387</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>1939334371</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1939334371</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>오늘더예쁜네일</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>0507-1439-1987</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>경기도 김포시 태장로 808 송호프라자 101호</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DC4EjlJyYZ7/?igsh=ZnU0a2toaHJhOWJo</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>6</v>
+      </c>
+      <c r="R272" t="n">
+        <v>48</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>1852304016</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1852304016</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>아이보리네일</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>0507-1467-7060</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강2로 262 5층</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>4</v>
+      </c>
+      <c r="R273" t="n">
+        <v>19</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>1198894552</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1198894552</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>예쁨, 시작</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>0507-1386-3437</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>경기도 김포시 사우중로74번길 29 2층 202호</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>6</v>
+      </c>
+      <c r="R274" t="n">
+        <v>8</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>1267215253</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1267215253</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>고촌다온네일</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>0507-1338-9461</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>경기도 김포시 고촌읍 은행영사정로23번길 52-12 1층</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/daon_nail._</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>9</v>
+      </c>
+      <c r="R275" t="n">
+        <v>154</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>2070781096</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2070781096</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>리아뜨네일</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>riattenail1441@naver.com</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>0507-1349-7184</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>경기도 김포시 솔터로 22 예미지아파트상가 애비뉴 스완 218호 리아뜨</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sarWGZlf</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>60</v>
+      </c>
+      <c r="R276" t="n">
+        <v>178</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>1565965774</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1565965774</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>핑쥬네일</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강8로148번길 97 1층 핑쥬네일</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ping__ju_nail</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>3</v>
+      </c>
+      <c r="R277" t="n">
+        <v>173</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>1919682907</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1919682907</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>네일즈영</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>0507-1382-1508</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>경기도 김포시 유현로33번길 73 꿈의그린더포레듀4단지 근린생활시설동 201호(cu2층)</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nails_yeong</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>359</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>13</v>
+      </c>
+      <c r="R278" t="n">
+        <v>372</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>1465517453</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1465517453</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>재둥이</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>0507-1349-6950</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강8로148번길 97</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>0</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>1399979243</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1399979243</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>단이네일</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>0507-1367-8973</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강9로75번길 132 111호</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>120</v>
+      </c>
+      <c r="R280" t="n">
+        <v>311</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>1009818943</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1009818943</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>로아네일</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>0507-1305-8596</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>경기도 김포시 고촌읍 장차로5번길 5-33 101호 로아네일</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/loanail2026</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>8</v>
+      </c>
+      <c r="R281" t="n">
+        <v>65</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>2089838885</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2089838885</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>네호네일</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>0507-1390-8850</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강7로22번길 174-77 102호</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>85</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>1446824309</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1446824309</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>네일새벽</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>nailsaebyuck@naver.com</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>0507-1351-3009</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>경기도 김포시 솔터로 22 301동 2층 265호</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.saebyuck_/</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>654</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>228</v>
+      </c>
+      <c r="R283" t="n">
+        <v>882</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>1569020780</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1569020780</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>네일아티즘</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>0507-1329-9327</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>경기도 김포시 걸포2로 83 파인스타 2층 C블럭 239호</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail__artism</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>15</v>
+      </c>
+      <c r="R284" t="n">
+        <v>92</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>1466190053</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1466190053</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>구래동네일 뮤즈인뷰티</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>0507-1444-6697</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강4로 487 2050호</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_muse_in_beauty_</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>10</v>
+      </c>
+      <c r="R285" t="n">
+        <v>138</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>1440975056</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1440975056</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>치즈네일샵</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>0507-1443-8682</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강8로148번길 52 102호</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cheese_nail_shop/?igsh=YTQwZjQ0NmI0OA%3D%3D</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>27</v>
+      </c>
+      <c r="R286" t="n">
+        <v>178</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>1918314526</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1918314526</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>채블리네일</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>0507-1421-8113</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강2로 229 정문상가 1층 F동 101호</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/chaevely_nail</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>0</v>
+      </c>
+      <c r="R287" t="n">
+        <v>54</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>1440231364</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1440231364</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>모모아이</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>경기도 김포시 통진읍 조강로 65</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>0</v>
+      </c>
+      <c r="R288" t="n">
+        <v>3</v>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>36747035</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36747035</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>더네일</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>0507-1378-6696</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>경기도 김포시 홍도평로 20 농협하나로마트건물 2층 더네일</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/the_nail_love</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>29</v>
+      </c>
+      <c r="R289" t="n">
+        <v>57</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>1695044754</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1695044754</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>네일 또만나</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>0507-1461-9337</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>경기도 김포시 통진읍 서암로6번길 5-1 101호 네일또만나</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_pWgPn/chat</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>15</v>
+      </c>
+      <c r="R290" t="n">
+        <v>50</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>2038733792</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038733792</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>오드네일</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>경기도 김포시 솔터로 22 301동 2층 216호</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>2</v>
+      </c>
+      <c r="R291" t="n">
+        <v>16</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>37942003</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37942003</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>그날엔네일</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>0507-1373-4115</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>경기도 김포시 풍무1로 65-1 씨티프라자 101호</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>http://instagram.com/gnal_n.nail</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>50</v>
+      </c>
+      <c r="R292" t="n">
+        <v>362</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>1105043154</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1105043154</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>제이네일</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>morningapple6@naver.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>0507-1437-3206</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>경기도 김포시 양촌읍 양곡2로60번길 28-16 1층 101호</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/j.nail213/</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>0</v>
+      </c>
+      <c r="R293" t="n">
+        <v>20</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>1151338104</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1151338104</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>뮤토뷰티샵</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>ithgml123@naver.com</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강8로 365 상가동 201호</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mutonail55</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>335</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>120</v>
+      </c>
+      <c r="R294" t="n">
+        <v>455</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>1222705451</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1222705451</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>르미네일</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2yoomi3574@naver.com</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>경기도 김포시 사우중로 87 상지프라자 205호</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reumynail</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>16</v>
+      </c>
+      <c r="R295" t="n">
+        <v>122</v>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>1389929181</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1389929181</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>속눈썹증모,연장</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>사월</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>zioxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>0507-1416-9944</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>경기도 김포시 고촌읍 태리로 285 5층 506호</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>16</v>
+      </c>
+      <c r="R296" t="n">
+        <v>58</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>1147960403</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1147960403</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>피부,체형관리</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>피부미인손발미인</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>bogdongyi66@naver.com</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>0507-1417-9073</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강2로 103 우남퍼스트빌</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bogdongyi66</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
         <v>25</v>
       </c>
-      <c r="Q240" t="n">
+      <c r="Q297" t="n">
         <v>15</v>
       </c>
-      <c r="R240" t="n">
+      <c r="R297" t="n">
         <v>40</v>
       </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T240" t="inlineStr">
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
         <is>
           <t>33261296</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="U297" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/33261296</t>
         </is>
       </c>
-      <c r="V240" t="inlineStr">
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>피부,체형관리</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>베라스킨뷰티 김포양곡</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>0507-1398-7933</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>경기도 김포시 양촌읍 양곡3로1번길 97 1층</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>184</v>
+      </c>
+      <c r="R298" t="n">
+        <v>240</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>1721866297</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1721866297</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
